--- a/2022 data/excel_outputs/157_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/157_boothwise_data.xlsx
@@ -14,11 +14,68 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="449">
   <si>
     <t>AC 157 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -829,7 +886,7 @@
     <t>P.P. BARAULI ROOM NO. 1</t>
   </si>
   <si>
-    <t>P.P. BARAULI ROOM NO. ■</t>
+    <t>CHNCHAN CHAMLAMHAMNAD DAN THIMPEMTAP</t>
   </si>
   <si>
     <t>P.P. ALISABAD ROOM NO. 1</t>
@@ -1310,8 +1367,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1327,7 +1392,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1335,12 +1400,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1639,70 +1722,127 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>412</v>
+        <v>431</v>
       </c>
       <c r="D2" t="s">
-        <v>413</v>
+        <v>432</v>
       </c>
       <c r="E2" t="s">
-        <v>414</v>
+        <v>433</v>
       </c>
       <c r="F2" t="s">
-        <v>415</v>
+        <v>434</v>
       </c>
       <c r="G2" t="s">
-        <v>416</v>
+        <v>435</v>
       </c>
       <c r="H2" t="s">
-        <v>417</v>
+        <v>436</v>
       </c>
       <c r="I2" t="s">
-        <v>418</v>
+        <v>437</v>
       </c>
       <c r="J2" t="s">
-        <v>419</v>
+        <v>438</v>
       </c>
       <c r="K2" t="s">
-        <v>420</v>
+        <v>439</v>
       </c>
       <c r="L2" t="s">
-        <v>421</v>
+        <v>440</v>
       </c>
       <c r="M2" t="s">
-        <v>422</v>
+        <v>441</v>
       </c>
       <c r="N2" t="s">
-        <v>423</v>
+        <v>442</v>
       </c>
       <c r="O2" t="s">
-        <v>424</v>
+        <v>443</v>
       </c>
       <c r="P2" t="s">
-        <v>425</v>
+        <v>444</v>
       </c>
       <c r="Q2" t="s">
-        <v>426</v>
+        <v>445</v>
       </c>
       <c r="R2" t="s">
-        <v>427</v>
+        <v>446</v>
       </c>
       <c r="S2" t="s">
-        <v>428</v>
+        <v>447</v>
       </c>
       <c r="T2" t="s">
-        <v>429</v>
+        <v>448</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -1710,7 +1850,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1772,7 +1912,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1834,7 +1974,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1896,7 +2036,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1958,7 +2098,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -2020,7 +2160,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -2082,7 +2222,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -2144,7 +2284,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -2206,7 +2346,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -2268,7 +2408,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -2330,7 +2470,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -2392,7 +2532,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -2454,7 +2594,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -2516,7 +2656,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -2578,7 +2718,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -2640,7 +2780,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -2702,7 +2842,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -2764,7 +2904,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -2826,7 +2966,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -2888,7 +3028,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -2950,7 +3090,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -3012,7 +3152,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -3074,7 +3214,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -3136,7 +3276,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -3198,7 +3338,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -3260,7 +3400,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -3322,7 +3462,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -3384,7 +3524,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -3446,7 +3586,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -3508,7 +3648,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -3570,7 +3710,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -3632,7 +3772,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -3694,7 +3834,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -3756,7 +3896,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -3818,7 +3958,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -3880,7 +4020,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -3942,7 +4082,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -4004,7 +4144,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -4066,7 +4206,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -4128,7 +4268,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -4190,7 +4330,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -4252,7 +4392,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -4314,7 +4454,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -4376,7 +4516,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -4438,7 +4578,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -4500,7 +4640,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -4562,7 +4702,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -4624,7 +4764,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -4686,7 +4826,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -4748,7 +4888,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -4810,7 +4950,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -4872,7 +5012,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -4934,7 +5074,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -4996,7 +5136,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -5058,7 +5198,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -5120,7 +5260,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -5182,7 +5322,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -5244,7 +5384,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -5306,7 +5446,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -5368,7 +5508,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -5430,7 +5570,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -5492,7 +5632,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -5554,7 +5694,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -5616,7 +5756,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -5678,7 +5818,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -5740,7 +5880,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -5802,7 +5942,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -5864,7 +6004,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -5926,7 +6066,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -5988,7 +6128,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -6050,7 +6190,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -6112,7 +6252,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -6174,7 +6314,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -6236,7 +6376,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -6298,7 +6438,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -6360,7 +6500,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -6422,7 +6562,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -6484,7 +6624,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -6546,7 +6686,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -6608,7 +6748,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -6670,7 +6810,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -6732,7 +6872,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -6794,7 +6934,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -6856,7 +6996,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -6918,7 +7058,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -6980,7 +7120,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -7042,7 +7182,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -7104,7 +7244,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -7166,7 +7306,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -7228,7 +7368,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -7290,7 +7430,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -7352,7 +7492,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -7414,7 +7554,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -7476,7 +7616,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -7538,7 +7678,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -7600,7 +7740,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -7662,7 +7802,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -7724,7 +7864,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -7786,7 +7926,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -7848,7 +7988,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -7910,7 +8050,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -7972,7 +8112,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -8034,7 +8174,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -8096,7 +8236,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -8158,7 +8298,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -8220,7 +8360,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -8282,7 +8422,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -8344,7 +8484,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -8406,7 +8546,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -8468,7 +8608,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -8530,7 +8670,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -8592,7 +8732,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -8654,7 +8794,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -8716,7 +8856,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -8778,7 +8918,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -8840,7 +8980,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -8902,7 +9042,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -8964,7 +9104,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -9026,7 +9166,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -9088,7 +9228,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -9150,7 +9290,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -9212,7 +9352,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -9274,7 +9414,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -9336,7 +9476,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -9398,7 +9538,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="C127">
         <v>0</v>
@@ -9460,7 +9600,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="C128">
         <v>0</v>
@@ -9522,7 +9662,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -9584,7 +9724,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -9646,7 +9786,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -9708,7 +9848,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -9770,7 +9910,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -9832,7 +9972,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -9894,7 +10034,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -9956,7 +10096,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -10018,7 +10158,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -10080,7 +10220,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -10142,7 +10282,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -10204,7 +10344,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -10266,7 +10406,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -10328,7 +10468,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -10390,7 +10530,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -10452,7 +10592,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -10514,7 +10654,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -10576,7 +10716,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -10638,7 +10778,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -10700,7 +10840,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -10762,7 +10902,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -10824,7 +10964,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -10886,7 +11026,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -10948,7 +11088,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -11010,7 +11150,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -11072,7 +11212,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -11134,7 +11274,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -11196,7 +11336,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -11258,7 +11398,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -11320,7 +11460,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -11382,7 +11522,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -11444,7 +11584,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -11506,7 +11646,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -11568,7 +11708,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -11630,7 +11770,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -11692,7 +11832,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -11754,7 +11894,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -11816,7 +11956,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -11878,7 +12018,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -11940,7 +12080,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -12002,7 +12142,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -12064,7 +12204,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -12126,7 +12266,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -12188,7 +12328,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -12250,7 +12390,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -12312,7 +12452,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -12374,7 +12514,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -12436,7 +12576,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -12498,7 +12638,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -12560,7 +12700,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -12622,7 +12762,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -12684,7 +12824,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -12746,7 +12886,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -12808,7 +12948,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -12870,7 +13010,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -12932,7 +13072,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -12994,7 +13134,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -13056,7 +13196,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -13118,7 +13258,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -13180,7 +13320,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -13242,7 +13382,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -13304,7 +13444,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="C190">
         <v>0</v>
@@ -13366,7 +13506,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="C191">
         <v>0</v>
@@ -13428,7 +13568,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="C192">
         <v>0</v>
@@ -13490,7 +13630,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="C193">
         <v>0</v>
@@ -13552,7 +13692,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="C194">
         <v>0</v>
@@ -13614,7 +13754,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="C195">
         <v>0</v>
@@ -13676,7 +13816,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="C196">
         <v>0</v>
@@ -13738,7 +13878,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="C197">
         <v>0</v>
@@ -13800,7 +13940,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="C198">
         <v>0</v>
@@ -13862,7 +14002,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="C199">
         <v>0</v>
@@ -13924,7 +14064,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="C200">
         <v>0</v>
@@ -13986,7 +14126,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="C201">
         <v>0</v>
@@ -14048,7 +14188,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="C202">
         <v>0</v>
@@ -14110,7 +14250,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="C203">
         <v>0</v>
@@ -14172,7 +14312,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="C204">
         <v>0</v>
@@ -14234,7 +14374,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
       <c r="C205">
         <v>0</v>
@@ -14296,7 +14436,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="C206">
         <v>0</v>
@@ -14358,7 +14498,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="C207">
         <v>0</v>
@@ -14420,7 +14560,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="C208">
         <v>0</v>
@@ -14482,7 +14622,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="C209">
         <v>0</v>
@@ -14544,7 +14684,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="C210">
         <v>0</v>
@@ -14606,7 +14746,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="C211">
         <v>0</v>
@@ -14668,7 +14808,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="C212">
         <v>0</v>
@@ -14730,7 +14870,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="C213">
         <v>0</v>
@@ -14792,7 +14932,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="C214">
         <v>0</v>
@@ -14854,7 +14994,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="C215">
         <v>0</v>
@@ -14916,7 +15056,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="C216">
         <v>0</v>
@@ -14978,7 +15118,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="C217">
         <v>0</v>
@@ -15040,7 +15180,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="C218">
         <v>0</v>
@@ -15102,7 +15242,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="C219">
         <v>0</v>
@@ -15164,7 +15304,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="C220">
         <v>0</v>
@@ -15226,7 +15366,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="C221">
         <v>0</v>
@@ -15288,7 +15428,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="C222">
         <v>0</v>
@@ -15350,7 +15490,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="C223">
         <v>0</v>
@@ -15412,7 +15552,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="C224">
         <v>0</v>
@@ -15474,7 +15614,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="C225">
         <v>0</v>
@@ -15536,7 +15676,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="C226">
         <v>0</v>
@@ -15598,7 +15738,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="C227">
         <v>0</v>
@@ -15660,7 +15800,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="C228">
         <v>0</v>
@@ -15722,7 +15862,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="C229">
         <v>0</v>
@@ -15784,7 +15924,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="C230">
         <v>0</v>
@@ -15846,7 +15986,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C231">
         <v>0</v>
@@ -15908,7 +16048,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="C232">
         <v>0</v>
@@ -15970,7 +16110,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="C233">
         <v>0</v>
@@ -16032,7 +16172,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="C234">
         <v>0</v>
@@ -16094,7 +16234,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="C235">
         <v>0</v>
@@ -16156,7 +16296,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="C236">
         <v>0</v>
@@ -16218,7 +16358,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="C237">
         <v>0</v>
@@ -16280,7 +16420,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="C238">
         <v>0</v>
@@ -16342,7 +16482,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="C239">
         <v>0</v>
@@ -16404,7 +16544,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>238</v>
+        <v>257</v>
       </c>
       <c r="C240">
         <v>0</v>
@@ -16466,7 +16606,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>239</v>
+        <v>258</v>
       </c>
       <c r="C241">
         <v>0</v>
@@ -16528,7 +16668,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="C242">
         <v>0</v>
@@ -16590,7 +16730,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="C243">
         <v>0</v>
@@ -16652,7 +16792,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="C244">
         <v>0</v>
@@ -16714,7 +16854,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>243</v>
+        <v>262</v>
       </c>
       <c r="C245">
         <v>0</v>
@@ -16776,7 +16916,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>244</v>
+        <v>263</v>
       </c>
       <c r="C246">
         <v>0</v>
@@ -16838,7 +16978,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="C247">
         <v>0</v>
@@ -16900,7 +17040,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="C248">
         <v>0</v>
@@ -16962,7 +17102,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="C249">
         <v>0</v>
@@ -17024,7 +17164,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="C250">
         <v>0</v>
@@ -17086,7 +17226,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>249</v>
+        <v>268</v>
       </c>
       <c r="C251">
         <v>0</v>
@@ -17148,7 +17288,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="C252">
         <v>0</v>
@@ -17210,7 +17350,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>251</v>
+        <v>270</v>
       </c>
       <c r="C253">
         <v>0</v>
@@ -17272,7 +17412,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>252</v>
+        <v>271</v>
       </c>
       <c r="C254">
         <v>0</v>
@@ -17334,7 +17474,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="C255">
         <v>0</v>
@@ -17396,7 +17536,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>254</v>
+        <v>273</v>
       </c>
       <c r="C256">
         <v>0</v>
@@ -17458,7 +17598,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="C257">
         <v>0</v>
@@ -17520,7 +17660,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="C258">
         <v>0</v>
@@ -17582,7 +17722,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="C259">
         <v>0</v>
@@ -17644,7 +17784,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="C260">
         <v>0</v>
@@ -17706,7 +17846,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>259</v>
+        <v>278</v>
       </c>
       <c r="C261">
         <v>0</v>
@@ -17768,7 +17908,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="C262">
         <v>0</v>
@@ -17830,7 +17970,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="C263">
         <v>0</v>
@@ -17892,7 +18032,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>262</v>
+        <v>281</v>
       </c>
       <c r="C264">
         <v>0</v>
@@ -17954,7 +18094,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="C265">
         <v>0</v>
@@ -18016,7 +18156,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="C266">
         <v>0</v>
@@ -18078,7 +18218,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>265</v>
+        <v>284</v>
       </c>
       <c r="C267">
         <v>0</v>
@@ -18140,7 +18280,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="C268">
         <v>0</v>
@@ -18202,7 +18342,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>267</v>
+        <v>286</v>
       </c>
       <c r="C269">
         <v>0</v>
@@ -18264,7 +18404,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>268</v>
+        <v>287</v>
       </c>
       <c r="C270">
         <v>0</v>
@@ -18326,7 +18466,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>269</v>
+        <v>288</v>
       </c>
       <c r="C271">
         <v>0</v>
@@ -18388,7 +18528,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>270</v>
+        <v>289</v>
       </c>
       <c r="C272">
         <v>0</v>
@@ -18450,7 +18590,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>271</v>
+        <v>290</v>
       </c>
       <c r="C273">
         <v>0</v>
@@ -18512,7 +18652,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>272</v>
+        <v>291</v>
       </c>
       <c r="C274">
         <v>0</v>
@@ -18574,7 +18714,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>273</v>
+        <v>292</v>
       </c>
       <c r="C275">
         <v>0</v>
@@ -18636,7 +18776,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="C276">
         <v>0</v>
@@ -18698,7 +18838,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="C277">
         <v>0</v>
@@ -18760,7 +18900,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="C278">
         <v>0</v>
@@ -18822,7 +18962,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="C279">
         <v>0</v>
@@ -18884,7 +19024,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>278</v>
+        <v>297</v>
       </c>
       <c r="C280">
         <v>0</v>
@@ -18946,7 +19086,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>279</v>
+        <v>298</v>
       </c>
       <c r="C281">
         <v>0</v>
@@ -19008,7 +19148,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>280</v>
+        <v>299</v>
       </c>
       <c r="C282">
         <v>0</v>
@@ -19070,7 +19210,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="C283">
         <v>0</v>
@@ -19132,7 +19272,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>282</v>
+        <v>301</v>
       </c>
       <c r="C284">
         <v>0</v>
@@ -19194,7 +19334,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="C285">
         <v>0</v>
@@ -19256,7 +19396,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="C286">
         <v>0</v>
@@ -19318,7 +19458,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="C287">
         <v>0</v>
@@ -19380,7 +19520,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="C288">
         <v>0</v>
@@ -19442,7 +19582,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>287</v>
+        <v>306</v>
       </c>
       <c r="C289">
         <v>0</v>
@@ -19504,7 +19644,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>288</v>
+        <v>307</v>
       </c>
       <c r="C290">
         <v>0</v>
@@ -19566,7 +19706,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>289</v>
+        <v>308</v>
       </c>
       <c r="C291">
         <v>0</v>
@@ -19628,7 +19768,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>290</v>
+        <v>309</v>
       </c>
       <c r="C292">
         <v>0</v>
@@ -19690,7 +19830,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>291</v>
+        <v>310</v>
       </c>
       <c r="C293">
         <v>0</v>
@@ -19752,7 +19892,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>292</v>
+        <v>311</v>
       </c>
       <c r="C294">
         <v>0</v>
@@ -19814,7 +19954,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="C295">
         <v>0</v>
@@ -19876,7 +20016,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>294</v>
+        <v>313</v>
       </c>
       <c r="C296">
         <v>0</v>
@@ -19938,7 +20078,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
       <c r="C297">
         <v>0</v>
@@ -20000,7 +20140,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
       <c r="C298">
         <v>0</v>
@@ -20062,7 +20202,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>297</v>
+        <v>316</v>
       </c>
       <c r="C299">
         <v>0</v>
@@ -20124,7 +20264,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>298</v>
+        <v>317</v>
       </c>
       <c r="C300">
         <v>0</v>
@@ -20186,7 +20326,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="C301">
         <v>0</v>
@@ -20248,7 +20388,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>300</v>
+        <v>319</v>
       </c>
       <c r="C302">
         <v>0</v>
@@ -20310,7 +20450,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
       <c r="C303">
         <v>0</v>
@@ -20372,7 +20512,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>302</v>
+        <v>321</v>
       </c>
       <c r="C304">
         <v>0</v>
@@ -20434,7 +20574,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>303</v>
+        <v>322</v>
       </c>
       <c r="C305">
         <v>0</v>
@@ -20496,7 +20636,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="C306">
         <v>0</v>
@@ -20558,7 +20698,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>305</v>
+        <v>324</v>
       </c>
       <c r="C307">
         <v>0</v>
@@ -20620,7 +20760,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>306</v>
+        <v>325</v>
       </c>
       <c r="C308">
         <v>0</v>
@@ -20682,7 +20822,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>307</v>
+        <v>326</v>
       </c>
       <c r="C309">
         <v>0</v>
@@ -20744,7 +20884,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="C310">
         <v>0</v>
@@ -20806,7 +20946,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>309</v>
+        <v>328</v>
       </c>
       <c r="C311">
         <v>0</v>
@@ -20868,7 +21008,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>310</v>
+        <v>329</v>
       </c>
       <c r="C312">
         <v>0</v>
@@ -20930,7 +21070,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>311</v>
+        <v>330</v>
       </c>
       <c r="C313">
         <v>0</v>
@@ -20992,7 +21132,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="C314">
         <v>0</v>
@@ -21054,7 +21194,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>313</v>
+        <v>332</v>
       </c>
       <c r="C315">
         <v>0</v>
@@ -21116,7 +21256,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>314</v>
+        <v>333</v>
       </c>
       <c r="C316">
         <v>0</v>
@@ -21178,7 +21318,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="C317">
         <v>0</v>
@@ -21240,7 +21380,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="C318">
         <v>0</v>
@@ -21302,7 +21442,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="C319">
         <v>0</v>
@@ -21364,7 +21504,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>318</v>
+        <v>337</v>
       </c>
       <c r="C320">
         <v>0</v>
@@ -21426,7 +21566,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>319</v>
+        <v>338</v>
       </c>
       <c r="C321">
         <v>0</v>
@@ -21488,7 +21628,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>320</v>
+        <v>339</v>
       </c>
       <c r="C322">
         <v>0</v>
@@ -21550,7 +21690,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>321</v>
+        <v>340</v>
       </c>
       <c r="C323">
         <v>0</v>
@@ -21612,7 +21752,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>322</v>
+        <v>341</v>
       </c>
       <c r="C324">
         <v>0</v>
@@ -21674,7 +21814,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>323</v>
+        <v>342</v>
       </c>
       <c r="C325">
         <v>0</v>
@@ -21736,7 +21876,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>324</v>
+        <v>343</v>
       </c>
       <c r="C326">
         <v>0</v>
@@ -21798,7 +21938,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>325</v>
+        <v>344</v>
       </c>
       <c r="C327">
         <v>0</v>
@@ -21860,7 +22000,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>326</v>
+        <v>345</v>
       </c>
       <c r="C328">
         <v>0</v>
@@ -21922,7 +22062,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>327</v>
+        <v>346</v>
       </c>
       <c r="C329">
         <v>0</v>
@@ -21984,7 +22124,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>328</v>
+        <v>347</v>
       </c>
       <c r="C330">
         <v>0</v>
@@ -22046,7 +22186,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>329</v>
+        <v>348</v>
       </c>
       <c r="C331">
         <v>0</v>
@@ -22108,7 +22248,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>330</v>
+        <v>349</v>
       </c>
       <c r="C332">
         <v>0</v>
@@ -22170,7 +22310,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>331</v>
+        <v>350</v>
       </c>
       <c r="C333">
         <v>0</v>
@@ -22232,7 +22372,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="C334">
         <v>0</v>
@@ -22294,7 +22434,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>333</v>
+        <v>352</v>
       </c>
       <c r="C335">
         <v>0</v>
@@ -22356,7 +22496,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>334</v>
+        <v>353</v>
       </c>
       <c r="C336">
         <v>0</v>
@@ -22418,7 +22558,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>335</v>
+        <v>354</v>
       </c>
       <c r="C337">
         <v>0</v>
@@ -22480,7 +22620,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="C338">
         <v>0</v>
@@ -22542,7 +22682,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>337</v>
+        <v>356</v>
       </c>
       <c r="C339">
         <v>0</v>
@@ -22604,7 +22744,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>338</v>
+        <v>357</v>
       </c>
       <c r="C340">
         <v>0</v>
@@ -22666,7 +22806,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="C341">
         <v>0</v>
@@ -22728,7 +22868,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>340</v>
+        <v>359</v>
       </c>
       <c r="C342">
         <v>0</v>
@@ -22790,7 +22930,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="C343">
         <v>0</v>
@@ -22852,7 +22992,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="C344">
         <v>0</v>
@@ -22914,7 +23054,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>343</v>
+        <v>362</v>
       </c>
       <c r="C345">
         <v>0</v>
@@ -22976,7 +23116,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="C346">
         <v>0</v>
@@ -23038,7 +23178,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>345</v>
+        <v>364</v>
       </c>
       <c r="C347">
         <v>0</v>
@@ -23100,7 +23240,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>346</v>
+        <v>365</v>
       </c>
       <c r="C348">
         <v>0</v>
@@ -23162,7 +23302,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>347</v>
+        <v>366</v>
       </c>
       <c r="C349">
         <v>0</v>
@@ -23224,7 +23364,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>348</v>
+        <v>367</v>
       </c>
       <c r="C350">
         <v>0</v>
@@ -23286,7 +23426,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="C351">
         <v>0</v>
@@ -23348,7 +23488,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="C352">
         <v>0</v>
@@ -23410,7 +23550,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>351</v>
+        <v>370</v>
       </c>
       <c r="C353">
         <v>0</v>
@@ -23472,7 +23612,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>352</v>
+        <v>371</v>
       </c>
       <c r="C354">
         <v>0</v>
@@ -23534,7 +23674,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="C355">
         <v>0</v>
@@ -23596,7 +23736,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>354</v>
+        <v>373</v>
       </c>
       <c r="C356">
         <v>0</v>
@@ -23658,7 +23798,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>355</v>
+        <v>374</v>
       </c>
       <c r="C357">
         <v>0</v>
@@ -23720,7 +23860,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="C358">
         <v>0</v>
@@ -23782,7 +23922,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>357</v>
+        <v>376</v>
       </c>
       <c r="C359">
         <v>0</v>
@@ -23844,7 +23984,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>358</v>
+        <v>377</v>
       </c>
       <c r="C360">
         <v>0</v>
@@ -23906,7 +24046,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>359</v>
+        <v>378</v>
       </c>
       <c r="C361">
         <v>0</v>
@@ -23968,7 +24108,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>360</v>
+        <v>379</v>
       </c>
       <c r="C362">
         <v>0</v>
@@ -24030,7 +24170,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="C363">
         <v>0</v>
@@ -24092,7 +24232,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>362</v>
+        <v>381</v>
       </c>
       <c r="C364">
         <v>0</v>
@@ -24154,7 +24294,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>363</v>
+        <v>382</v>
       </c>
       <c r="C365">
         <v>0</v>
@@ -24216,7 +24356,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>364</v>
+        <v>383</v>
       </c>
       <c r="C366">
         <v>0</v>
@@ -24278,7 +24418,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>365</v>
+        <v>384</v>
       </c>
       <c r="C367">
         <v>0</v>
@@ -24340,7 +24480,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>366</v>
+        <v>385</v>
       </c>
       <c r="C368">
         <v>0</v>
@@ -24402,7 +24542,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="C369">
         <v>0</v>
@@ -24464,7 +24604,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>368</v>
+        <v>387</v>
       </c>
       <c r="C370">
         <v>0</v>
@@ -24526,7 +24666,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>369</v>
+        <v>388</v>
       </c>
       <c r="C371">
         <v>0</v>
@@ -24588,7 +24728,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="C372">
         <v>0</v>
@@ -24650,7 +24790,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="C373">
         <v>0</v>
@@ -24712,7 +24852,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="C374">
         <v>0</v>
@@ -24774,7 +24914,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>373</v>
+        <v>392</v>
       </c>
       <c r="C375">
         <v>0</v>
@@ -24836,7 +24976,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="C376">
         <v>0</v>
@@ -24898,7 +25038,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>375</v>
+        <v>394</v>
       </c>
       <c r="C377">
         <v>0</v>
@@ -24960,7 +25100,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>376</v>
+        <v>395</v>
       </c>
       <c r="C378">
         <v>0</v>
@@ -25022,7 +25162,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>377</v>
+        <v>396</v>
       </c>
       <c r="C379">
         <v>0</v>
@@ -25084,7 +25224,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="C380">
         <v>0</v>
@@ -25146,7 +25286,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>379</v>
+        <v>398</v>
       </c>
       <c r="C381">
         <v>0</v>
@@ -25208,7 +25348,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>380</v>
+        <v>399</v>
       </c>
       <c r="C382">
         <v>0</v>
@@ -25270,7 +25410,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="C383">
         <v>0</v>
@@ -25332,7 +25472,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="C384">
         <v>0</v>
@@ -25394,7 +25534,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>383</v>
+        <v>402</v>
       </c>
       <c r="C385">
         <v>0</v>
@@ -25456,7 +25596,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>384</v>
+        <v>403</v>
       </c>
       <c r="C386">
         <v>0</v>
@@ -25518,7 +25658,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="C387">
         <v>0</v>
@@ -25580,7 +25720,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>386</v>
+        <v>405</v>
       </c>
       <c r="C388">
         <v>0</v>
@@ -25642,7 +25782,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="C389">
         <v>0</v>
@@ -25704,7 +25844,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>388</v>
+        <v>407</v>
       </c>
       <c r="C390">
         <v>0</v>
@@ -25766,7 +25906,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>389</v>
+        <v>408</v>
       </c>
       <c r="C391">
         <v>0</v>
@@ -25828,7 +25968,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>390</v>
+        <v>409</v>
       </c>
       <c r="C392">
         <v>0</v>
@@ -25890,7 +26030,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>391</v>
+        <v>410</v>
       </c>
       <c r="C393">
         <v>0</v>
@@ -25952,7 +26092,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>392</v>
+        <v>411</v>
       </c>
       <c r="C394">
         <v>0</v>
@@ -26014,7 +26154,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="C395">
         <v>0</v>
@@ -26076,7 +26216,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="C396">
         <v>0</v>
@@ -26138,7 +26278,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>395</v>
+        <v>414</v>
       </c>
       <c r="C397">
         <v>0</v>
@@ -26200,7 +26340,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
       <c r="C398">
         <v>0</v>
@@ -26262,7 +26402,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>397</v>
+        <v>416</v>
       </c>
       <c r="C399">
         <v>0</v>
@@ -26324,7 +26464,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>398</v>
+        <v>417</v>
       </c>
       <c r="C400">
         <v>0</v>
@@ -26386,7 +26526,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>399</v>
+        <v>418</v>
       </c>
       <c r="C401">
         <v>0</v>
@@ -26448,7 +26588,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>400</v>
+        <v>419</v>
       </c>
       <c r="C402">
         <v>0</v>
@@ -26510,7 +26650,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>401</v>
+        <v>420</v>
       </c>
       <c r="C403">
         <v>0</v>
@@ -26572,7 +26712,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>402</v>
+        <v>421</v>
       </c>
       <c r="C404">
         <v>0</v>
@@ -26634,7 +26774,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>403</v>
+        <v>422</v>
       </c>
       <c r="C405">
         <v>0</v>
@@ -26696,7 +26836,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>404</v>
+        <v>423</v>
       </c>
       <c r="C406">
         <v>0</v>
@@ -26758,7 +26898,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
       <c r="C407">
         <v>0</v>
@@ -26820,7 +26960,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>406</v>
+        <v>425</v>
       </c>
       <c r="C408">
         <v>0</v>
@@ -26882,7 +27022,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>407</v>
+        <v>426</v>
       </c>
       <c r="C409">
         <v>0</v>
@@ -26944,7 +27084,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>408</v>
+        <v>427</v>
       </c>
       <c r="C410">
         <v>0</v>
@@ -27006,7 +27146,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>409</v>
+        <v>428</v>
       </c>
       <c r="C411">
         <v>0</v>
@@ -27068,7 +27208,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>410</v>
+        <v>429</v>
       </c>
       <c r="C412">
         <v>0</v>
@@ -27130,7 +27270,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>411</v>
+        <v>430</v>
       </c>
       <c r="C413">
         <v>0</v>
